--- a/evaluation/CB016639_Results_Workbook.xlsx
+++ b/evaluation/CB016639_Results_Workbook.xlsx
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,12 +285,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Config comparison'!$A$5:$A$8</f>
+              <f>'2. Config comparison'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Config comparison'!$B$5:$B$8</f>
+              <f>'2. Config comparison'!$B$5:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -309,12 +309,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Config comparison'!$A$5:$A$8</f>
+              <f>'2. Config comparison'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Config comparison'!$C$5:$C$8</f>
+              <f>'2. Config comparison'!$C$5:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -333,12 +333,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Config comparison'!$A$5:$A$8</f>
+              <f>'2. Config comparison'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Config comparison'!$D$5:$D$8</f>
+              <f>'2. Config comparison'!$D$5:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Config comparison'!$A$5:$A$8</f>
+              <f>'2. Config comparison'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Config comparison'!$E$5:$E$8</f>
+              <f>'2. Config comparison'!$E$5:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Config comparison'!$A$5:$A$8</f>
+              <f>'2. Config comparison'!$A$5:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Config comparison'!$F$5:$F$8</f>
+              <f>'2. Config comparison'!$F$5:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -532,6 +532,30 @@
           <val>
             <numRef>
               <f>'3. By attack type'!$E$5:$E$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'3. By attack type'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'3. By attack type'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'3. By attack type'!$F$5:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -1169,7 +1193,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -1880,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2066,106 +2090,119 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>ModSecurity (OWASP CRS)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.663594470046083</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.3865546218487395</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Hybrid (proposed)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>0.9447004608294931</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>0.9361702127659574</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>0.03305785123966942</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J9" s="5" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>McNemar exact test - hybrid vs each baseline</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Baseline correct only</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Hybrid correct only</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>No detection</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>1.180999849430483e-21</v>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>significant</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Rules only</t>
+          <t>No detection</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>0.0224609375</v>
+        <v>88</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>1.180999849430483e-21</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
@@ -2176,19 +2213,61 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ML only</t>
+          <t>Rules only</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.0224609375</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D34" s="13" t="n">
         <v>1.407861402565253e-21</v>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ModSecurity (OWASP CRS)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>3.114746823093192e-15</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>significant</t>
         </is>
@@ -2206,14 +2285,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2253,7 +2333,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>ModSecurity (OWASP CRS)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Hybrid (proposed)</t>
         </is>
       </c>
     </row>
@@ -2273,6 +2358,9 @@
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>0.8666666666666667</v>
       </c>
     </row>
@@ -2292,6 +2380,9 @@
         <v>0</v>
       </c>
       <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2313,6 +2404,9 @@
       <c r="E7" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="F7" s="15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2330,6 +2424,9 @@
         <v>1</v>
       </c>
       <c r="E8" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2349,6 +2446,9 @@
         <v>0.5</v>
       </c>
       <c r="E9" s="15" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2370,6 +2470,9 @@
       <c r="E10" s="16" t="n">
         <v>1</v>
       </c>
+      <c r="F10" s="16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2389,6 +2492,9 @@
       <c r="E11" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="F11" s="15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2406,6 +2512,9 @@
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16" t="n">
         <v>1</v>
       </c>
     </row>
